--- a/re_generation_monthly_en.xlsx
+++ b/re_generation_monthly_en.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -281,6 +281,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -572,9 +576,13 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="47.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
